--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/102.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/102.xlsx
@@ -426,13 +426,13 @@
         <v>-11.01120570335433</v>
       </c>
       <c r="E2">
-        <v>-9.213612650343673</v>
+        <v>-11.72352842604298</v>
       </c>
       <c r="F2">
-        <v>-3.322241340873774</v>
+        <v>-3.588226800443084</v>
       </c>
       <c r="G2">
-        <v>-9.116290128705874</v>
+        <v>-10.90912930768034</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-10.52135379443492</v>
       </c>
       <c r="E3">
-        <v>-10.58913663017354</v>
+        <v>-11.7213547585193</v>
       </c>
       <c r="F3">
-        <v>-2.78999706049223</v>
+        <v>-3.789706461988994</v>
       </c>
       <c r="G3">
-        <v>-8.813146784220349</v>
+        <v>-10.44051165495989</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-9.929890380267549</v>
       </c>
       <c r="E4">
-        <v>-9.966589194443069</v>
+        <v>-13.19813541716068</v>
       </c>
       <c r="F4">
-        <v>-3.23945098916838</v>
+        <v>-3.789586348715588</v>
       </c>
       <c r="G4">
-        <v>-8.648606049827492</v>
+        <v>-10.17298978047692</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-9.29821935834439</v>
       </c>
       <c r="E5">
-        <v>-11.45956367613588</v>
+        <v>-13.06198231764606</v>
       </c>
       <c r="F5">
-        <v>-3.177694542554871</v>
+        <v>-3.418601179004427</v>
       </c>
       <c r="G5">
-        <v>-7.985106512846762</v>
+        <v>-8.93637853137418</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-8.633395422564014</v>
       </c>
       <c r="E6">
-        <v>-11.72915279076051</v>
+        <v>-13.61209681162385</v>
       </c>
       <c r="F6">
-        <v>-3.051398334854448</v>
+        <v>-3.842513227182657</v>
       </c>
       <c r="G6">
-        <v>-7.640144357109165</v>
+        <v>-9.314548769416206</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-7.946305975686061</v>
       </c>
       <c r="E7">
-        <v>-13.14602173828041</v>
+        <v>-15.0153576947507</v>
       </c>
       <c r="F7">
-        <v>-2.934359132880308</v>
+        <v>-3.763206160406035</v>
       </c>
       <c r="G7">
-        <v>-7.260411541572602</v>
+        <v>-8.913496040606738</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-7.24874592215758</v>
       </c>
       <c r="E8">
-        <v>-13.15376995730754</v>
+        <v>-15.80840670534398</v>
       </c>
       <c r="F8">
-        <v>-2.802250271114441</v>
+        <v>-3.555262748016081</v>
       </c>
       <c r="G8">
-        <v>-6.821668251798531</v>
+        <v>-8.53982814449812</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-6.553194354482393</v>
       </c>
       <c r="E9">
-        <v>-14.05584650810948</v>
+        <v>-16.43723060604908</v>
       </c>
       <c r="F9">
-        <v>-3.243777552113202</v>
+        <v>-3.627676141266605</v>
       </c>
       <c r="G9">
-        <v>-6.216182714847989</v>
+        <v>-7.672710193578975</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-5.857343370156176</v>
       </c>
       <c r="E10">
-        <v>-16.07277448943776</v>
+        <v>-16.49599661324662</v>
       </c>
       <c r="F10">
-        <v>-3.054931321827388</v>
+        <v>-3.925546290537071</v>
       </c>
       <c r="G10">
-        <v>-6.465344303770156</v>
+        <v>-7.181041212268576</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-5.180521923969388</v>
       </c>
       <c r="E11">
-        <v>-15.86220950502911</v>
+        <v>-17.39854412534536</v>
       </c>
       <c r="F11">
-        <v>-2.751540932184666</v>
+        <v>-3.774686504241433</v>
       </c>
       <c r="G11">
-        <v>-5.454131547708693</v>
+        <v>-6.853740816982991</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-4.532130084776364</v>
       </c>
       <c r="E12">
-        <v>-16.65471962721547</v>
+        <v>-18.27955874353763</v>
       </c>
       <c r="F12">
-        <v>-2.570193083628993</v>
+        <v>-3.528338322322889</v>
       </c>
       <c r="G12">
-        <v>-5.645623433336756</v>
+        <v>-6.482297607476763</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-3.917590829291143</v>
       </c>
       <c r="E13">
-        <v>-17.31133930137965</v>
+        <v>-18.65996867407797</v>
       </c>
       <c r="F13">
-        <v>-2.241872148631617</v>
+        <v>-3.415627340028376</v>
       </c>
       <c r="G13">
-        <v>-4.724679322494601</v>
+        <v>-6.055343170368037</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-3.359228101395876</v>
       </c>
       <c r="E14">
-        <v>-17.89621889031433</v>
+        <v>-19.88538279750158</v>
       </c>
       <c r="F14">
-        <v>-2.837059097747479</v>
+        <v>-3.295229108235885</v>
       </c>
       <c r="G14">
-        <v>-4.471942344390021</v>
+        <v>-5.315088635059303</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-2.863225314378563</v>
       </c>
       <c r="E15">
-        <v>-19.06932008200133</v>
+        <v>-21.29583489735262</v>
       </c>
       <c r="F15">
-        <v>-2.490345921305746</v>
+        <v>-3.306071609171128</v>
       </c>
       <c r="G15">
-        <v>-3.63001764502473</v>
+        <v>-5.260666576939224</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-2.434029393913943</v>
       </c>
       <c r="E16">
-        <v>-19.18173492076774</v>
+        <v>-21.63942380573659</v>
       </c>
       <c r="F16">
-        <v>-2.295283622029324</v>
+        <v>-3.043797235566359</v>
       </c>
       <c r="G16">
-        <v>-3.936163654314372</v>
+        <v>-5.329559029611458</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-2.080222088603719</v>
       </c>
       <c r="E17">
-        <v>-20.26101065948982</v>
+        <v>-22.5862914929484</v>
       </c>
       <c r="F17">
-        <v>-2.376601964859943</v>
+        <v>-2.677778128434981</v>
       </c>
       <c r="G17">
-        <v>-2.536359062853257</v>
+        <v>-4.584077142896215</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-1.794271181448069</v>
       </c>
       <c r="E18">
-        <v>-21.62070762266289</v>
+        <v>-23.26196245726285</v>
       </c>
       <c r="F18">
-        <v>-1.668224408723348</v>
+        <v>-2.469987135647142</v>
       </c>
       <c r="G18">
-        <v>-2.31204642874886</v>
+        <v>-4.757059768414213</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-1.569878406567744</v>
       </c>
       <c r="E19">
-        <v>-20.88929567178802</v>
+        <v>-24.56123146327757</v>
       </c>
       <c r="F19">
-        <v>-1.21321130640701</v>
+        <v>-2.145344980285599</v>
       </c>
       <c r="G19">
-        <v>-1.849983656196162</v>
+        <v>-4.415563753856232</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-1.399774044078031</v>
       </c>
       <c r="E20">
-        <v>-22.00811857401909</v>
+        <v>-24.95394072922274</v>
       </c>
       <c r="F20">
-        <v>-0.6699439409964135</v>
+        <v>-1.648978948854107</v>
       </c>
       <c r="G20">
-        <v>-2.863176118490109</v>
+        <v>-4.177005842296351</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-1.26834334718358</v>
       </c>
       <c r="E21">
-        <v>-23.99564317361557</v>
+        <v>-25.3762798006001</v>
       </c>
       <c r="F21">
-        <v>-0.7412870835625209</v>
+        <v>-1.568742453851544</v>
       </c>
       <c r="G21">
-        <v>-2.490948309691075</v>
+        <v>-4.416560228063553</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-1.170165540522708</v>
       </c>
       <c r="E22">
-        <v>-24.33929548063565</v>
+        <v>-25.98540936784585</v>
       </c>
       <c r="F22">
-        <v>-0.914513618101148</v>
+        <v>-1.407452693587258</v>
       </c>
       <c r="G22">
-        <v>-2.162565366014148</v>
+        <v>-4.314436519268115</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-1.101508706338209</v>
       </c>
       <c r="E23">
-        <v>-25.36864932189717</v>
+        <v>-25.8357206595223</v>
       </c>
       <c r="F23">
-        <v>0.2232920847489186</v>
+        <v>-1.205863687544179</v>
       </c>
       <c r="G23">
-        <v>-2.749813107588846</v>
+        <v>-4.414812260018818</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-1.05697570132411</v>
       </c>
       <c r="E24">
-        <v>-25.57560058404771</v>
+        <v>-26.7545933204187</v>
       </c>
       <c r="F24">
-        <v>-0.4262738708911193</v>
+        <v>-1.029064404397278</v>
       </c>
       <c r="G24">
-        <v>-2.682489853502227</v>
+        <v>-3.542241840596493</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-1.041789081824692</v>
       </c>
       <c r="E25">
-        <v>-24.48989894070874</v>
+        <v>-27.50415992359031</v>
       </c>
       <c r="F25">
-        <v>-0.1963522145700886</v>
+        <v>-1.261581335791279</v>
       </c>
       <c r="G25">
-        <v>-2.045828909208367</v>
+        <v>-3.840846427147676</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-1.058077970618483</v>
       </c>
       <c r="E26">
-        <v>-26.5665620226722</v>
+        <v>-26.91487412944618</v>
       </c>
       <c r="F26">
-        <v>-0.1474271790259442</v>
+        <v>-0.8351112890732041</v>
       </c>
       <c r="G26">
-        <v>-1.28410548607746</v>
+        <v>-4.604960064157937</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-1.105250560022381</v>
       </c>
       <c r="E27">
-        <v>-25.626545916634</v>
+        <v>-27.88999496599185</v>
       </c>
       <c r="F27">
-        <v>-0.1847385035828395</v>
+        <v>-0.6677744467684816</v>
       </c>
       <c r="G27">
-        <v>-1.51135788462073</v>
+        <v>-4.63924076321709</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-1.186568237187172</v>
       </c>
       <c r="E28">
-        <v>-25.57912826529968</v>
+        <v>-26.96448356220021</v>
       </c>
       <c r="F28">
-        <v>5.618173588261423E-05</v>
+        <v>-0.5006082481487358</v>
       </c>
       <c r="G28">
-        <v>-3.065543146214678</v>
+        <v>-4.284207927949031</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-1.298046388344812</v>
       </c>
       <c r="E29">
-        <v>-24.6156863632198</v>
+        <v>-27.25059707847883</v>
       </c>
       <c r="F29">
-        <v>0.07251347845875537</v>
+        <v>-0.704573011903044</v>
       </c>
       <c r="G29">
-        <v>-2.394469081040095</v>
+        <v>-4.942423834249085</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-1.433225442978014</v>
       </c>
       <c r="E30">
-        <v>-24.02153245951742</v>
+        <v>-26.19467920868831</v>
       </c>
       <c r="F30">
-        <v>-0.3757732805468503</v>
+        <v>-0.6573088530015126</v>
       </c>
       <c r="G30">
-        <v>-2.063560191116704</v>
+        <v>-4.78864237285886</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-1.586398394405244</v>
       </c>
       <c r="E31">
-        <v>-25.00139460834912</v>
+        <v>-26.83975580260694</v>
       </c>
       <c r="F31">
-        <v>-0.2228864792165623</v>
+        <v>-0.7217666057155506</v>
       </c>
       <c r="G31">
-        <v>-2.393168036643161</v>
+        <v>-4.792290594043137</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-1.746045343165971</v>
       </c>
       <c r="E32">
-        <v>-25.29490312268226</v>
+        <v>-26.76383140739434</v>
       </c>
       <c r="F32">
-        <v>-0.4187771458957838</v>
+        <v>-0.5938343723945977</v>
       </c>
       <c r="G32">
-        <v>-2.814074107051639</v>
+        <v>-4.563909299470975</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-1.902314436811792</v>
       </c>
       <c r="E33">
-        <v>-24.60732227172763</v>
+        <v>-26.11074394295614</v>
       </c>
       <c r="F33">
-        <v>-0.258568405092151</v>
+        <v>-0.7461454583799401</v>
       </c>
       <c r="G33">
-        <v>-2.976489471208283</v>
+        <v>-4.906074044227887</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-2.046570301060121</v>
       </c>
       <c r="E34">
-        <v>-23.90481104196972</v>
+        <v>-24.97650611520296</v>
       </c>
       <c r="F34">
-        <v>-0.4674205365229764</v>
+        <v>-1.112723713508208</v>
       </c>
       <c r="G34">
-        <v>-3.154649789949702</v>
+        <v>-4.791409988929691</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-2.167561553200287</v>
       </c>
       <c r="E35">
-        <v>-22.5773749276273</v>
+        <v>-24.85286066089753</v>
       </c>
       <c r="F35">
-        <v>-0.4500852918845911</v>
+        <v>-1.197780478427661</v>
       </c>
       <c r="G35">
-        <v>-2.474004937621085</v>
+        <v>-5.025359621098906</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-2.259485973921104</v>
       </c>
       <c r="E36">
-        <v>-22.83076569072649</v>
+        <v>-24.62168206280596</v>
       </c>
       <c r="F36">
-        <v>-0.6123947724217235</v>
+        <v>-0.9305284450994707</v>
       </c>
       <c r="G36">
-        <v>-3.47984467827231</v>
+        <v>-4.925450667269241</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-2.318135031191927</v>
       </c>
       <c r="E37">
-        <v>-22.89849807645922</v>
+        <v>-24.10046376147112</v>
       </c>
       <c r="F37">
-        <v>-0.5507087370374527</v>
+        <v>-1.086088388038593</v>
       </c>
       <c r="G37">
-        <v>-2.409942570890648</v>
+        <v>-5.163035278440578</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-2.339243815262117</v>
       </c>
       <c r="E38">
-        <v>-21.30957428749189</v>
+        <v>-23.28774758826253</v>
       </c>
       <c r="F38">
-        <v>-0.6762792948930242</v>
+        <v>-0.8972794342859043</v>
       </c>
       <c r="G38">
-        <v>-2.675557571142993</v>
+        <v>-4.834665576945808</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-2.325583496828375</v>
       </c>
       <c r="E39">
-        <v>-20.97997836379162</v>
+        <v>-22.90949321134984</v>
       </c>
       <c r="F39">
-        <v>-0.5865662768024349</v>
+        <v>-1.313478553576668</v>
       </c>
       <c r="G39">
-        <v>-3.147187820304184</v>
+        <v>-4.833500264915984</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-2.280707747067851</v>
       </c>
       <c r="E40">
-        <v>-19.88239400465652</v>
+        <v>-22.59268569824723</v>
       </c>
       <c r="F40">
-        <v>-0.8154458469307438</v>
+        <v>-1.241678980571618</v>
       </c>
       <c r="G40">
-        <v>-1.873908968808475</v>
+        <v>-4.591165020895795</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-2.209008264754947</v>
       </c>
       <c r="E41">
-        <v>-19.59879831992616</v>
+        <v>-21.99193833638968</v>
       </c>
       <c r="F41">
-        <v>-0.6722898774811417</v>
+        <v>-1.466019097332586</v>
       </c>
       <c r="G41">
-        <v>-2.680318135628465</v>
+        <v>-4.085793691598351</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-2.120662475531143</v>
       </c>
       <c r="E42">
-        <v>-19.41685329124599</v>
+        <v>-20.73007452567833</v>
       </c>
       <c r="F42">
-        <v>-0.6555295198202993</v>
+        <v>-1.274104594186802</v>
       </c>
       <c r="G42">
-        <v>-2.920031427581553</v>
+        <v>-4.627183756363065</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-2.023318640017911</v>
       </c>
       <c r="E43">
-        <v>-18.03983491499358</v>
+        <v>-19.83451897744743</v>
       </c>
       <c r="F43">
-        <v>-0.5365370275103587</v>
+        <v>-1.670952222580767</v>
       </c>
       <c r="G43">
-        <v>-3.128390542732202</v>
+        <v>-4.681744857395794</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-1.92474859084202</v>
       </c>
       <c r="E44">
-        <v>-18.83982607624061</v>
+        <v>-20.1693090608345</v>
       </c>
       <c r="F44">
-        <v>-0.886963775018842</v>
+        <v>-1.56455422826299</v>
       </c>
       <c r="G44">
-        <v>-3.475041076694828</v>
+        <v>-3.969676306808414</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-1.837514990599585</v>
       </c>
       <c r="E45">
-        <v>-18.44955312931157</v>
+        <v>-19.00841663507217</v>
       </c>
       <c r="F45">
-        <v>-0.6290573827290356</v>
+        <v>-1.601678341786853</v>
       </c>
       <c r="G45">
-        <v>-2.651033049788072</v>
+        <v>-4.927864054967371</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-1.769444915164947</v>
       </c>
       <c r="E46">
-        <v>-17.90057981078371</v>
+        <v>-18.1405662908202</v>
       </c>
       <c r="F46">
-        <v>-0.7792602736742531</v>
+        <v>-1.790661252694129</v>
       </c>
       <c r="G46">
-        <v>-3.395591294297859</v>
+        <v>-4.613309260007979</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-1.729959411869266</v>
       </c>
       <c r="E47">
-        <v>-16.86480459337931</v>
+        <v>-18.65723347577734</v>
       </c>
       <c r="F47">
-        <v>-0.6454971622049945</v>
+        <v>-1.669424713090005</v>
       </c>
       <c r="G47">
-        <v>-3.325129643040011</v>
+        <v>-4.817235554681545</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-1.728688574235119</v>
       </c>
       <c r="E48">
-        <v>-15.56480650304936</v>
+        <v>-16.52754196318405</v>
       </c>
       <c r="F48">
-        <v>-0.6412989962076067</v>
+        <v>-1.593360704695343</v>
       </c>
       <c r="G48">
-        <v>-3.281691975019233</v>
+        <v>-4.207582040897059</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-1.766160716771622</v>
       </c>
       <c r="E49">
-        <v>-14.87929516471624</v>
+        <v>-17.30626741049106</v>
       </c>
       <c r="F49">
-        <v>-0.956275760713285</v>
+        <v>-1.421288085948816</v>
       </c>
       <c r="G49">
-        <v>-3.466165504104042</v>
+        <v>-4.692014169658613</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-1.845353248407672</v>
       </c>
       <c r="E50">
-        <v>-13.88784012242491</v>
+        <v>-16.42474107473593</v>
       </c>
       <c r="F50">
-        <v>-0.7001180520107884</v>
+        <v>-1.701383955857412</v>
       </c>
       <c r="G50">
-        <v>-2.949233749783464</v>
+        <v>-4.13435939465946</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-1.96577362990319</v>
       </c>
       <c r="E51">
-        <v>-13.89158969890326</v>
+        <v>-15.26875298632391</v>
       </c>
       <c r="F51">
-        <v>-1.013718069893014</v>
+        <v>-1.612185353923962</v>
       </c>
       <c r="G51">
-        <v>-3.050834392383696</v>
+        <v>-5.210670718205151</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-2.118128298171188</v>
       </c>
       <c r="E52">
-        <v>-13.36129180718304</v>
+        <v>-15.11478034158911</v>
       </c>
       <c r="F52">
-        <v>-0.4739397879830085</v>
+        <v>-1.825876807721942</v>
       </c>
       <c r="G52">
-        <v>-3.913579112645464</v>
+        <v>-4.857779805900999</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-2.299539103283367</v>
       </c>
       <c r="E53">
-        <v>-12.27414558063562</v>
+        <v>-14.94986237517777</v>
       </c>
       <c r="F53">
-        <v>-0.8255618696537315</v>
+        <v>-1.76182329830047</v>
       </c>
       <c r="G53">
-        <v>-3.04536537115282</v>
+        <v>-5.741844439435673</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-2.502595005372599</v>
       </c>
       <c r="E54">
-        <v>-11.42886967931189</v>
+        <v>-14.05281695899835</v>
       </c>
       <c r="F54">
-        <v>-1.236406422052799</v>
+        <v>-1.772810763531202</v>
       </c>
       <c r="G54">
-        <v>-3.218374481035132</v>
+        <v>-5.037386833043079</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-2.715917597219314</v>
       </c>
       <c r="E55">
-        <v>-10.65231337105455</v>
+        <v>-13.96416755182419</v>
       </c>
       <c r="F55">
-        <v>-0.7413102778497993</v>
+        <v>-1.969600208842462</v>
       </c>
       <c r="G55">
-        <v>-3.948876149185173</v>
+        <v>-5.695155815695331</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-2.937194349516049</v>
       </c>
       <c r="E56">
-        <v>-12.06347191285078</v>
+        <v>-13.52298550010092</v>
       </c>
       <c r="F56">
-        <v>-0.8528317245538911</v>
+        <v>-1.852553551561697</v>
       </c>
       <c r="G56">
-        <v>-4.17646291282791</v>
+        <v>-5.798610363797557</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-3.15970916204366</v>
       </c>
       <c r="E57">
-        <v>-10.89204625654661</v>
+        <v>-12.48504114364684</v>
       </c>
       <c r="F57">
-        <v>-1.206217400425174</v>
+        <v>-1.827277577000076</v>
       </c>
       <c r="G57">
-        <v>-3.896682088213024</v>
+        <v>-5.932240534490238</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-3.377121444634199</v>
       </c>
       <c r="E58">
-        <v>-10.34384730707407</v>
+        <v>-11.96503194487204</v>
       </c>
       <c r="F58">
-        <v>-0.8153878612125479</v>
+        <v>-1.810344918919451</v>
       </c>
       <c r="G58">
-        <v>-4.710026847937787</v>
+        <v>-5.443309374340815</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-3.589894059935317</v>
       </c>
       <c r="E59">
-        <v>-10.08900290381841</v>
+        <v>-12.35251082333836</v>
       </c>
       <c r="F59">
-        <v>-1.200219192061503</v>
+        <v>-1.845909216623842</v>
       </c>
       <c r="G59">
-        <v>-4.56034053137964</v>
+        <v>-5.971516846768151</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-3.792155629728494</v>
       </c>
       <c r="E60">
-        <v>-9.586066052052537</v>
+        <v>-11.96788941197088</v>
       </c>
       <c r="F60">
-        <v>-0.7035069030556411</v>
+        <v>-2.153650191866067</v>
       </c>
       <c r="G60">
-        <v>-4.656733685846599</v>
+        <v>-6.075103816691946</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-3.98173277791049</v>
       </c>
       <c r="E61">
-        <v>-10.45491266058619</v>
+        <v>-11.73193327380122</v>
       </c>
       <c r="F61">
-        <v>-1.025934003982098</v>
+        <v>-2.027254580077307</v>
       </c>
       <c r="G61">
-        <v>-5.340470587708896</v>
+        <v>-6.289378876721274</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-4.160899833380571</v>
       </c>
       <c r="E62">
-        <v>-7.086959743809535</v>
+        <v>-11.43866024011647</v>
       </c>
       <c r="F62">
-        <v>-1.091481059830818</v>
+        <v>-1.95629331488389</v>
       </c>
       <c r="G62">
-        <v>-4.880284894476965</v>
+        <v>-6.216871308320157</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-4.324230505734577</v>
       </c>
       <c r="E63">
-        <v>-8.951717413058073</v>
+        <v>-10.34803161705716</v>
       </c>
       <c r="F63">
-        <v>-1.549752959509768</v>
+        <v>-1.819823098742283</v>
       </c>
       <c r="G63">
-        <v>-5.301409460891035</v>
+        <v>-6.283105392924355</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-4.473296880827896</v>
       </c>
       <c r="E64">
-        <v>-8.986659118501258</v>
+        <v>-10.57885246570213</v>
       </c>
       <c r="F64">
-        <v>-1.205857888972359</v>
+        <v>-1.804084118089092</v>
       </c>
       <c r="G64">
-        <v>-5.126632519690752</v>
+        <v>-6.816056877109467</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-4.608637445428996</v>
       </c>
       <c r="E65">
-        <v>-7.153668694416527</v>
+        <v>-10.12706925632689</v>
       </c>
       <c r="F65">
-        <v>-1.24141307463532</v>
+        <v>-1.897416273362513</v>
       </c>
       <c r="G65">
-        <v>-6.443438423936798</v>
+        <v>-6.994571424223587</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-4.723241882877892</v>
       </c>
       <c r="E66">
-        <v>-7.630050574601426</v>
+        <v>-10.13100902871357</v>
       </c>
       <c r="F66">
-        <v>-1.332933590398818</v>
+        <v>-2.297715708723943</v>
       </c>
       <c r="G66">
-        <v>-5.612100849206096</v>
+        <v>-6.516770318177194</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-4.821024657314097</v>
       </c>
       <c r="E67">
-        <v>-7.431345663618858</v>
+        <v>-9.818431110334117</v>
       </c>
       <c r="F67">
-        <v>-1.384622887966104</v>
+        <v>-2.086065352206461</v>
       </c>
       <c r="G67">
-        <v>-6.084634877299509</v>
+        <v>-6.863589689962322</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.901774941645699</v>
       </c>
       <c r="E68">
-        <v>-7.099748154407196</v>
+        <v>-9.977638671021785</v>
       </c>
       <c r="F68">
-        <v>-1.176973546004143</v>
+        <v>-1.919097961763387</v>
       </c>
       <c r="G68">
-        <v>-6.466165319063895</v>
+        <v>-6.784629868305165</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-4.960056566413903</v>
       </c>
       <c r="E69">
-        <v>-7.114094360063496</v>
+        <v>-9.369582352115856</v>
       </c>
       <c r="F69">
-        <v>-1.476425048646553</v>
+        <v>-2.102460399842669</v>
       </c>
       <c r="G69">
-        <v>-6.197362263457232</v>
+        <v>-6.402801477442244</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-4.999847940757867</v>
       </c>
       <c r="E70">
-        <v>-8.147840821112462</v>
+        <v>-9.728626942288008</v>
       </c>
       <c r="F70">
-        <v>-1.91232274477589</v>
+        <v>-2.345340207445692</v>
       </c>
       <c r="G70">
-        <v>-6.128036129319354</v>
+        <v>-6.274140435604009</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-5.01740710345115</v>
       </c>
       <c r="E71">
-        <v>-9.074624726100254</v>
+        <v>-9.406960376575167</v>
       </c>
       <c r="F71">
-        <v>-1.386225778890521</v>
+        <v>-2.029454723899143</v>
       </c>
       <c r="G71">
-        <v>-5.807293924747065</v>
+        <v>-6.797233115173171</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-5.006686065759526</v>
       </c>
       <c r="E72">
-        <v>-7.668850539899145</v>
+        <v>-9.386011655815683</v>
       </c>
       <c r="F72">
-        <v>-1.699538353283975</v>
+        <v>-2.058152684201729</v>
       </c>
       <c r="G72">
-        <v>-5.321259491944505</v>
+        <v>-7.281390468654964</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-4.970260813106649</v>
       </c>
       <c r="E73">
-        <v>-7.790222700252726</v>
+        <v>-10.5604170480169</v>
       </c>
       <c r="F73">
-        <v>-1.869184683907703</v>
+        <v>-2.525181255695673</v>
       </c>
       <c r="G73">
-        <v>-5.204572693321813</v>
+        <v>-6.642051293019834</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-4.903353647582675</v>
       </c>
       <c r="E74">
-        <v>-7.436739076161993</v>
+        <v>-10.09673300894951</v>
       </c>
       <c r="F74">
-        <v>-1.732515659589423</v>
+        <v>-2.388525485255839</v>
       </c>
       <c r="G74">
-        <v>-5.968249338320891</v>
+        <v>-7.128300911282446</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-4.806180160993646</v>
       </c>
       <c r="E75">
-        <v>-8.108298186077484</v>
+        <v>-10.76054389983788</v>
       </c>
       <c r="F75">
-        <v>-1.589878248133974</v>
+        <v>-2.274634079412337</v>
       </c>
       <c r="G75">
-        <v>-4.589764660132682</v>
+        <v>-6.886422522546676</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-4.685249468998228</v>
       </c>
       <c r="E76">
-        <v>-8.128554050313793</v>
+        <v>-11.55837497898325</v>
       </c>
       <c r="F76">
-        <v>-1.648582989235569</v>
+        <v>-2.015012138231333</v>
       </c>
       <c r="G76">
-        <v>-4.074743090588264</v>
+        <v>-6.681897019130502</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-4.540368029786679</v>
       </c>
       <c r="E77">
-        <v>-9.052394447196601</v>
+        <v>-11.33522989378128</v>
       </c>
       <c r="F77">
-        <v>-1.585741381324393</v>
+        <v>-2.312410946449606</v>
       </c>
       <c r="G77">
-        <v>-5.160840386748041</v>
+        <v>-5.85060248149181</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-4.378440908600636</v>
       </c>
       <c r="E78">
-        <v>-9.147913549440391</v>
+        <v>-12.20074354544529</v>
       </c>
       <c r="F78">
-        <v>-1.987704178430645</v>
+        <v>-2.358908037136145</v>
       </c>
       <c r="G78">
-        <v>-4.180475294021507</v>
+        <v>-5.86382148983012</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-4.207595265944523</v>
       </c>
       <c r="E79">
-        <v>-9.648699376052626</v>
+        <v>-13.00039959961576</v>
       </c>
       <c r="F79">
-        <v>-1.937345238912254</v>
+        <v>-2.513179040396511</v>
       </c>
       <c r="G79">
-        <v>-4.109934189670716</v>
+        <v>-6.288104316688655</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-4.028843807802207</v>
       </c>
       <c r="E80">
-        <v>-10.36982716245608</v>
+        <v>-13.35206730562941</v>
       </c>
       <c r="F80">
-        <v>-1.971958570838232</v>
+        <v>-2.457361988061075</v>
       </c>
       <c r="G80">
-        <v>-4.507577056574736</v>
+        <v>-5.827547842356326</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.85129468551342</v>
       </c>
       <c r="E81">
-        <v>-11.00525357826437</v>
+        <v>-13.41777546348071</v>
       </c>
       <c r="F81">
-        <v>-2.187974423568467</v>
+        <v>-2.522479949595144</v>
       </c>
       <c r="G81">
-        <v>-3.491977827673739</v>
+        <v>-5.797226555762141</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.676896204256113</v>
       </c>
       <c r="E82">
-        <v>-12.22954011166007</v>
+        <v>-14.24342042998119</v>
       </c>
       <c r="F82">
-        <v>-1.941937707793375</v>
+        <v>-2.502122820671346</v>
       </c>
       <c r="G82">
-        <v>-3.380581280822803</v>
+        <v>-5.832404412662437</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.499910123345023</v>
       </c>
       <c r="E83">
-        <v>-13.25302957908166</v>
+        <v>-15.68522315538733</v>
       </c>
       <c r="F83">
-        <v>-1.906942498494707</v>
+        <v>-2.480397228798124</v>
       </c>
       <c r="G83">
-        <v>-3.260670010844861</v>
+        <v>-5.634046455585925</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.326900443778993</v>
       </c>
       <c r="E84">
-        <v>-14.20532237815466</v>
+        <v>-16.39801402114266</v>
       </c>
       <c r="F84">
-        <v>-2.193317393316524</v>
+        <v>-2.554694329522614</v>
       </c>
       <c r="G84">
-        <v>-2.568699782226398</v>
+        <v>-4.864381033706306</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.160784972486452</v>
       </c>
       <c r="E85">
-        <v>-15.2900005863679</v>
+        <v>-17.13137774431483</v>
       </c>
       <c r="F85">
-        <v>-2.287691634782666</v>
+        <v>-2.59547982696685</v>
       </c>
       <c r="G85">
-        <v>-3.599699668976084</v>
+        <v>-4.682867132333606</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.00503762134551</v>
       </c>
       <c r="E86">
-        <v>-16.02324656921587</v>
+        <v>-18.3688693079169</v>
       </c>
       <c r="F86">
-        <v>-1.633204348402596</v>
+        <v>-2.68150909521719</v>
       </c>
       <c r="G86">
-        <v>-3.372629350437474</v>
+        <v>-4.444140382951222</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-2.875677758060404</v>
       </c>
       <c r="E87">
-        <v>-18.07859865249924</v>
+        <v>-19.40777370086061</v>
       </c>
       <c r="F87">
-        <v>-1.795406141177365</v>
+        <v>-2.656537959859799</v>
       </c>
       <c r="G87">
-        <v>-2.399616979353661</v>
+        <v>-4.840008797446192</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-2.780570536098591</v>
       </c>
       <c r="E88">
-        <v>-19.18809742674852</v>
+        <v>-21.05428156530947</v>
       </c>
       <c r="F88">
-        <v>-2.045291451905864</v>
+        <v>-2.188450734825077</v>
       </c>
       <c r="G88">
-        <v>-2.908808678203423</v>
+        <v>-4.760952969968396</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-2.730046991371692</v>
       </c>
       <c r="E89">
-        <v>-21.35265366072685</v>
+        <v>-23.3375019321848</v>
       </c>
       <c r="F89">
-        <v>-2.122776938763729</v>
+        <v>-2.710112621635857</v>
       </c>
       <c r="G89">
-        <v>-2.059193581550405</v>
+        <v>-4.203218741876301</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-2.739757163909908</v>
       </c>
       <c r="E90">
-        <v>-22.29157840452921</v>
+        <v>-23.98870102296181</v>
       </c>
       <c r="F90">
-        <v>-2.070878064243534</v>
+        <v>-2.447086090429347</v>
       </c>
       <c r="G90">
-        <v>-2.715578756167242</v>
+        <v>-4.586768616419642</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-2.812280994624634</v>
       </c>
       <c r="E91">
-        <v>-24.18178609770086</v>
+        <v>-26.05042014069996</v>
       </c>
       <c r="F91">
-        <v>-2.635134602906266</v>
+        <v>-2.632279220468816</v>
       </c>
       <c r="G91">
-        <v>-2.068287650146783</v>
+        <v>-4.30201535240477</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-2.954169359818434</v>
       </c>
       <c r="E92">
-        <v>-25.87872304869914</v>
+        <v>-27.78496153985794</v>
       </c>
       <c r="F92">
-        <v>-1.7764199603052</v>
+        <v>-2.808800172168376</v>
       </c>
       <c r="G92">
-        <v>-2.68147682656721</v>
+        <v>-5.095966936360482</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-3.168483028280888</v>
       </c>
       <c r="E93">
-        <v>-28.08834665600181</v>
+        <v>-29.26819074548624</v>
       </c>
       <c r="F93">
-        <v>-2.141341480627869</v>
+        <v>-2.427780159739702</v>
       </c>
       <c r="G93">
-        <v>-3.050930398204335</v>
+        <v>-4.940017067642035</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-3.441585365384977</v>
       </c>
       <c r="E94">
-        <v>-30.01528253761267</v>
+        <v>-31.8506911668175</v>
       </c>
       <c r="F94">
-        <v>-2.51771766539645</v>
+        <v>-2.50357991893287</v>
       </c>
       <c r="G94">
-        <v>-2.604327873320034</v>
+        <v>-4.88611807571716</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-3.765964383713613</v>
       </c>
       <c r="E95">
-        <v>-29.9717299388439</v>
+        <v>-33.19981187894565</v>
       </c>
       <c r="F95">
-        <v>-2.651537934216501</v>
+        <v>-2.596145005991298</v>
       </c>
       <c r="G95">
-        <v>-3.077408141427426</v>
+        <v>-5.211008393850157</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-4.126618294469433</v>
       </c>
       <c r="E96">
-        <v>-33.55496424570821</v>
+        <v>-35.54014536000572</v>
       </c>
       <c r="F96">
-        <v>-2.836649055883093</v>
+        <v>-2.907626888424566</v>
       </c>
       <c r="G96">
-        <v>-3.496261673601556</v>
+        <v>-4.725649312337608</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-4.496422951982472</v>
       </c>
       <c r="E97">
-        <v>-35.80577658834765</v>
+        <v>-38.4460739234388</v>
       </c>
       <c r="F97">
-        <v>-2.611053134139481</v>
+        <v>-2.787262619695589</v>
       </c>
       <c r="G97">
-        <v>-3.577906347691062</v>
+        <v>-5.639042068804685</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.866713759434904</v>
       </c>
       <c r="E98">
-        <v>-38.96948400619335</v>
+        <v>-39.86213227411132</v>
       </c>
       <c r="F98">
-        <v>-3.083012148414888</v>
+        <v>-2.596335530493942</v>
       </c>
       <c r="G98">
-        <v>-4.188476882589925</v>
+        <v>-5.490769355191808</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-5.212248767305294</v>
       </c>
       <c r="E99">
-        <v>-42.39987325835077</v>
+        <v>-42.00090111285299</v>
       </c>
       <c r="F99">
-        <v>-3.177930627264669</v>
+        <v>-2.791999224504797</v>
       </c>
       <c r="G99">
-        <v>-3.161068937750348</v>
+        <v>-5.340470587708896</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-5.524520639677456</v>
       </c>
       <c r="E100">
-        <v>-43.69688934854666</v>
+        <v>-44.80211097909569</v>
       </c>
       <c r="F100">
-        <v>-2.893629964419462</v>
+        <v>-3.252076965121851</v>
       </c>
       <c r="G100">
-        <v>-4.374003165156222</v>
+        <v>-5.956165847102551</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-5.781866912453895</v>
       </c>
       <c r="E101">
-        <v>-46.62524065102872</v>
+        <v>-47.37486386012544</v>
       </c>
       <c r="F101">
-        <v>-3.559192522974961</v>
+        <v>-3.490469506503909</v>
       </c>
       <c r="G101">
-        <v>-4.385901265824363</v>
+        <v>-6.053396569590945</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-6.003065685071209</v>
       </c>
       <c r="E102">
-        <v>-48.47162064063563</v>
+        <v>-49.33349453131598</v>
       </c>
       <c r="F102">
-        <v>-3.706855639463196</v>
+        <v>-3.113873804373587</v>
       </c>
       <c r="G102">
-        <v>-4.471462315286827</v>
+        <v>-6.495142524169136</v>
       </c>
     </row>
   </sheetData>
